--- a/packages/clients/src/time-tracking/teamleader-excel/__fixtures__/sample-timesheet.xlsx
+++ b/packages/clients/src/time-tracking/teamleader-excel/__fixtures__/sample-timesheet.xlsx
@@ -4,85 +4,15 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Export" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Export" state="visible" r:id="rId3"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="21">
-  <si>
-    <t>Projekt</t>
-  </si>
-  <si>
-    <t>Datum</t>
-  </si>
-  <si>
-    <t>Dauer (Stunden))</t>
-  </si>
-  <si>
-    <t>Beschreibung</t>
-  </si>
-  <si>
-    <t>Position</t>
-  </si>
-  <si>
-    <t>Aufgabe</t>
-  </si>
-  <si>
-    <t>ACME &gt; Development</t>
-  </si>
-  <si>
-    <t>ACME-100 Implement dashboard layout</t>
-  </si>
-  <si>
-    <t>Software-Entwicklung</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Worked on https://example.atlassian.net/browse/ACME-101 responsive grid</t>
-  </si>
-  <si>
-    <t>Daily</t>
-  </si>
-  <si>
-    <t>ACME-200 debug session timeout issue</t>
-  </si>
-  <si>
-    <t>ACME-100, ACME-102 integration testing and fixes</t>
-  </si>
-  <si>
-    <t>Code Review</t>
-  </si>
-  <si>
-    <t>ACME-300 CI pipeline setup</t>
-  </si>
-  <si>
-    <t>Sprint planning</t>
-  </si>
-  <si>
-    <t>ACME-400 quick look</t>
-  </si>
-  <si>
-    <t>Cross-ticket review: ACME-100, ACME-101, ACME-102, ACME-200</t>
-  </si>
-  <si>
-    <t>ACME-200 hotfix deployment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://example.atlassian.net/browse/ACME-500
-https://example.atlassian.net/browse/ACME-501
-ACME-502</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts x14ac:knownFonts="1" count="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -111,9 +41,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -453,267 +382,271 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="str">
+        <v>Export from time tracking system — sample data</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" t="str">
+        <v>Projekt</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Datum</v>
+      </c>
+      <c r="C2" t="str">
+        <v>Dauer (Stunden)</v>
+      </c>
+      <c r="D2" t="str">
+        <v>Beschreibung</v>
+      </c>
+      <c r="E2" t="str">
+        <v>Position</v>
+      </c>
+      <c r="F2" t="str">
+        <v>Aufgabe</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B3" t="str">
+        <v>10-03-2025</v>
+      </c>
+      <c r="C3">
+        <v>3.5</v>
+      </c>
+      <c r="D3" t="str">
+        <v>ACME-100 Implement dashboard layout</v>
+      </c>
+      <c r="E3" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B4" t="str">
+        <v>10-03-2025</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>Worked on https://example.atlassian.net/browse/ACME-101 responsive grid</v>
+      </c>
+      <c r="E4" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B5" t="str">
+        <v>11-03-2025</v>
+      </c>
+      <c r="C5">
+        <v>0.25</v>
+      </c>
+      <c r="D5" t="str">
+        <v>Daily</v>
+      </c>
+      <c r="E5" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B6" t="str">
+        <v>11-03-2025</v>
+      </c>
+      <c r="C6">
+        <v>6</v>
+      </c>
+      <c r="D6" t="str">
+        <v>ACME-200 debug session timeout issue</v>
+      </c>
+      <c r="E6" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B7" t="str">
+        <v>12-03-2025</v>
+      </c>
+      <c r="C7">
+        <v>4</v>
+      </c>
+      <c r="D7" t="str">
+        <v>ACME-100, ACME-102 integration testing and fixes</v>
+      </c>
+      <c r="E7" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B8" t="str">
+        <v>12-03-2025</v>
+      </c>
+      <c r="C8">
+        <v>0.5</v>
+      </c>
+      <c r="D8" t="str">
+        <v>Code Review</v>
+      </c>
+      <c r="E8" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B9" t="str">
+        <v>13-03-2025</v>
+      </c>
+      <c r="C9">
+        <v>1.5</v>
+      </c>
+      <c r="D9" t="str">
+        <v>ACME-300 CI pipeline setup</v>
+      </c>
+      <c r="E9" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B10" t="str">
+        <v>13-03-2025</v>
+      </c>
+      <c r="C10">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D10" t="str">
+        <v>Sprint planning</v>
+      </c>
+      <c r="E10" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B11" t="str">
+        <v>14-03-2025</v>
+      </c>
+      <c r="C11">
+        <v>0.05</v>
+      </c>
+      <c r="D11" t="str">
+        <v>ACME-400 quick look</v>
+      </c>
+      <c r="E11" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B12" t="str">
+        <v>14-03-2025</v>
+      </c>
+      <c r="C12">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="1">
-        <v>45726.375</v>
-      </c>
-      <c r="C2">
-        <v>3.5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="1">
-        <v>45726.54166666667</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-      <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1">
-        <v>45727.35416666667</v>
-      </c>
-      <c r="C4">
-        <v>0.25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="1">
-        <v>45727.375</v>
-      </c>
-      <c r="C5">
-        <v>6</v>
-      </c>
-      <c r="D5" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="1">
-        <v>45728.33333333333</v>
-      </c>
-      <c r="C6">
-        <v>4</v>
-      </c>
-      <c r="D6" t="s">
-        <v>13</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1">
-        <v>45728.58333333333</v>
-      </c>
-      <c r="C7">
-        <v>0.5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1">
-        <v>45729.41666666667</v>
-      </c>
-      <c r="C8">
+      <c r="D12" t="str">
+        <v>Cross-ticket review: ACME-100, ACME-101, ACME-102, ACME-200</v>
+      </c>
+      <c r="E12" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B13" t="str">
+        <v>15-03-2025</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="str">
+        <v>ACME-200 hotfix deployment</v>
+      </c>
+      <c r="E13" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="str">
+        <v>ACME &gt; Development</v>
+      </c>
+      <c r="B14" t="str">
+        <v>16-03-2025</v>
+      </c>
+      <c r="C14">
         <v>1.5</v>
       </c>
-      <c r="D8" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="1">
-        <v>45729.58333333333</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="1">
-        <v>45730.375</v>
-      </c>
-      <c r="C10">
-        <v>0.05</v>
-      </c>
-      <c r="D10" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="1">
-        <v>45730.41666666667</v>
-      </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="1">
-        <v>45731.66666666667</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" s="1">
-        <v>45732.375</v>
-      </c>
-      <c r="C13">
-        <v>1.5</v>
-      </c>
-      <c r="D13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>9</v>
+      <c r="D14" t="str">
+        <v>https://example.atlassian.net/browse/ACME-500 https://example.atlassian.net/browse/ACME-501 ACME-502</v>
+      </c>
+      <c r="E14" t="str">
+        <v>Software-Entwicklung</v>
+      </c>
+      <c r="F14" t="str">
+        <v/>
       </c>
     </row>
   </sheetData>
